--- a/lamaml_maml_comparison_results.xlsx
+++ b/lamaml_maml_comparison_results.xlsx
@@ -669,7 +669,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>300</v>
@@ -963,7 +963,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>500</v>
@@ -1063,8 +1063,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>8</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -1101,8 +1103,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -1139,8 +1143,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>8</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -1177,8 +1183,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>8</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -1215,8 +1223,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1322,8 +1332,10 @@
       <c r="A2" t="n">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>8</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>800</v>
@@ -1360,8 +1372,10 @@
       <c r="A3" t="n">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>8</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>800</v>
@@ -1398,8 +1412,10 @@
       <c r="A4" t="n">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>8</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>800</v>
@@ -1436,8 +1452,10 @@
       <c r="A5" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>8</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>800</v>
@@ -1474,8 +1492,10 @@
       <c r="A6" t="n">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
-        <v>8</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>800</v>
@@ -1578,8 +1598,10 @@
       <c r="A2" t="n">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>8</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>800</v>
@@ -1616,8 +1638,10 @@
       <c r="A3" t="n">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>8</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>800</v>
@@ -1654,8 +1678,10 @@
       <c r="A4" t="n">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>8</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>800</v>
@@ -1692,8 +1718,10 @@
       <c r="A5" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>8</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>800</v>
@@ -1730,8 +1758,10 @@
       <c r="A6" t="n">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
-        <v>8</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>800</v>
@@ -1834,8 +1864,10 @@
       <c r="A2" t="n">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>8</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>1200</v>
@@ -1872,8 +1904,10 @@
       <c r="A3" t="n">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>8</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>1200</v>
@@ -1910,8 +1944,10 @@
       <c r="A4" t="n">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>8</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>1200</v>
@@ -1948,8 +1984,10 @@
       <c r="A5" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>8</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>1200</v>
@@ -1986,8 +2024,10 @@
       <c r="A6" t="n">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
-        <v>8</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>1200</v>
